--- a/banks/W11_Kahoot匯入.xlsx
+++ b/banks/W11_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,30 +491,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>雙螺旋</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>鳥嘌呤</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>核苷酸</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>腺嘌呤</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>核苷酸</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>雙螺旋</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>鳥嘌呤</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -526,30 +526,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>核苷</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>基因</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>嘧啶</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>核苷</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>核糖</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>基因</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -566,25 +566,25 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>含氮鹼基</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>核糖核酸</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>胸腺嘧啶</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>含氮鹼基</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>核糖核酸</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -601,25 +601,25 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>核苷酸</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>核苷</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>嘌呤</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>核苷</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>核苷酸</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -631,30 +631,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>基因</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>核苷</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>嘧啶</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>互補</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>基因</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>核苷</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>嘧啶</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -666,30 +666,30 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>胞嘧啶</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>反平行</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>核苷酸</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>腺嘌呤</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>胞嘧啶</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -706,25 +706,25 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>腺嘌呤</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>鳥嘌呤</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>互補</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>腺嘌呤</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>鳥嘌呤</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -736,19 +736,19 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>反平行</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>胞嘧啶</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>基因</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>反平行</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>雙螺旋</t>
@@ -759,7 +759,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -781,20 +781,20 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>胸腺嘧啶</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>胞嘧啶</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>胸腺嘧啶</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -811,17 +811,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>胞嘧啶</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>胸腺嘧啶</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>雙螺旋</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>胞嘧啶</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -841,19 +841,19 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>含氮鹼基</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>雙螺旋</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>去氧核糖</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>雙螺旋</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>含氮鹼基</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>核糖核酸</t>
@@ -864,7 +864,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -876,30 +876,30 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>核糖</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>嘌呤</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>尿嘧啶</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>嘧啶</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>核糖</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>嘌呤</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>去氧核糖</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>雙螺旋</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>鳥嘌呤</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>去氧核糖</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>磷酸雙酯鍵</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>雙螺旋</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -946,30 +946,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>胞嘧啶</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>尿嘧啶</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>核苷酸</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>雙螺旋</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>尿嘧啶</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>胞嘧啶</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>核苷酸</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -981,30 +981,30 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>去氧核糖</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>鹼基配對</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>胸腺嘧啶</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>胞嘧啶</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>去氧核糖</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>鹼基配對</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1016,30 +1016,30 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>尿嘧啶</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>核糖</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>互補</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>核糖</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>嘧啶</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>尿嘧啶</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>鳥嘌呤</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>反平行</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>含氮鹼基</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>反平行</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>鳥嘌呤</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1091,25 +1091,25 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>核苷酸</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>磷酸雙酯鍵</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>去氧核糖核酸</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>磷酸雙酯鍵</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>核苷酸</t>
-        </is>
-      </c>
       <c r="F19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>胸腺嘧啶</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>鹼基配對</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>胸腺嘧啶</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1156,30 +1156,170 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>基因</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>嘌呤</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>核苷</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>核糖</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>基因</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>嘌呤</t>
-        </is>
-      </c>
       <c r="F21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:DNA雙股螺旋) 標號1是什麼?</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>大溝</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>雙螺旋</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>小溝</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>磷酸雙酯鍵</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:核苷酸結構) 標號3是什麼?</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>磷酸</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>含氮鹼基</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>核苷</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>去氧核糖</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>胸腺嘧啶—鳥嘌呤</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>腺嘌呤—胸腺嘧啶</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>鳥嘌呤—尿嘧啶</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>腺嘌呤—胞嘧啶</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>若DNA中A占30%，依鹼基互補原則，T約占多少%?</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
